--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
@@ -7250,7 +7250,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
@@ -7250,7 +7250,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250927_124918.xlsx
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
